--- a/Result/profitability/6968.xlsx
+++ b/Result/profitability/6968.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM16"/>
+  <dimension ref="A1:AM17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2462,6 +2462,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6968</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>912</v>
+      </c>
+      <c r="D17" t="n">
+        <v>535</v>
+      </c>
+      <c r="E17" t="n">
+        <v>377</v>
+      </c>
+      <c r="F17" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>40</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4.35%</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>36</v>
+      </c>
+      <c r="K17" t="n">
+        <v>26</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="N17" t="n">
+        <v>41.03875</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.4299999999999999</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.4479166666666666</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.1499999999999986</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.003645200486026789</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.3800000000000026</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.009117082533589338</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK17" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
